--- a/output/FSSAI_Restaurants_Maharashtra.xlsx
+++ b/output/FSSAI_Restaurants_Maharashtra.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -7014,6 +7014,5046 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai Masala</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>1012837220829</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Fast Food</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>494226</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>16/11/2025</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>16/11/2026</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Owner 961</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>9448981222</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>mumbaimasala785@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>37 Mumbai Masala Street, Thane, Mumbai</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtrian Cuisine</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>1071165662444</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>415030</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2025</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Owner 805</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>9673960129</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>maharashtriancu823@outlook.com</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>369 Maharashtrian Cuisine Street, Sangli, Sangli</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>The Golden Fork</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>1034315190589</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>490601</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>12/05/2025</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Owner 893</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>9107473294</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>thegoldenfork883@outlook.com</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>444 The Golden Fork Street, Nagpur, Nagpur</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Delights</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>1056570485602</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Malegaon</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>467523</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>22/12/2025</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>22/12/2026</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Owner 148</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>9666948953</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>coastaldelights850@gmail.com</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>44 Coastal Delights Street, Malegaon, Nashik</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Curry House</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>1057202892792</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>416131</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>08/01/2027</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Owner 978</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>9963112993</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>curryhouse138@gmail.com</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>192 Curry House Street, Nashik, Nashik</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Delights</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>1036773124403</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>478049</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Owner 34</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>9540351166</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>coastaldelights323@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>63 Coastal Delights Street, Nashik, Nashik</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Curry House</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>1054569819113</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Chiplun</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>456817</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>19/12/2025</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>19/12/2026</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Owner 353</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>9311669551</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>curryhouse873@outlook.com</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>141 Curry House Street, Chiplun, Ratnagiri</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Namaste Kitchen</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>1095804472775</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>430248</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>02/08/2024</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Owner 495</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>9848006035</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>namastekitchen646@gmail.com</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>40 Namaste Kitchen Street, Aurangabad, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Maharaja's Kitchen</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>1016924795740</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>443346</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>26/03/2027</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Owner 778</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>9274377392</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>maharajaskitche257@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>210 Maharaja's Kitchen Street, Aurangabad, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Spice Garden</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>1078751091908</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Paithan</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>449857</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2024</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2025</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Owner 362</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>9610313989</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>spicegarden488@outlook.com</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>433 Spice Garden Street, Paithan, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Royal Feast</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>1024727774156</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Food Truck</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>499016</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Owner 790</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>9150685902</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>royalfeast620@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>304 Royal Feast Street, Nagpur, Nagpur</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Tandoori Palace</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>1072548225482</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Malegaon</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>455954</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>16/02/2027</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Owner 781</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>9144072825</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>tandooripalace983@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>194 Tandoori Palace Street, Malegaon, Nashik</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Saffron Dreams</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>1074942874979</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>456902</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Owner 126</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>9238046392</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>saffrondreams461@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>263 Saffron Dreams Street, Thane, Mumbai</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>The Golden Fork</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>1068064147535</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Paithan</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>455321</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>25/06/2024</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>25/06/2025</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Owner 507</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>9236334537</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>thegoldenfork890@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>498 The Golden Fork Street, Paithan, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Taj Mahal Restaurant</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>1086547527322</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Paithan</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>478820</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>14/06/2024</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>14/06/2025</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Owner 339</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>9224597513</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>tajmahalrestaur739@outlook.com</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>335 Taj Mahal Restaurant Street, Paithan, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Curry House</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1071294864123</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>431517</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Owner 958</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>9602005334</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>curryhouse398@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>206 Curry House Street, Kolhapur, Kolhapur</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Taj Mahal Restaurant</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>1033508485596</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>428405</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2024</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Owner 488</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>9413602438</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>tajmahalrestaur378@gmail.com</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>469 Taj Mahal Restaurant Street, Navi Mumbai, Mumbai</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Delights</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1049611175590</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Pandharpur</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>478070</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Owner 201</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>9271575941</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>coastaldelights831@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>471 Coastal Delights Street, Pandharpur, Solapur</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Taj Mahal Restaurant</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>1062803548898</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Food Truck</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Karad</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>447483</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2025</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Owner 17</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>9221282183</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>tajmahalrestaur306@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>280 Taj Mahal Restaurant Street, Karad, Satara</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Spice Route</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>1075637965776</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>490803</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>17/03/2025</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>17/03/2026</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Owner 809</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>9539978933</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>spiceroute568@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>462 Spice Route Street, Solapur, Solapur</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Spice Garden</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1033117783054</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Food Truck</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>447583</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2024</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>21/10/2025</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Owner 538</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>9501926532</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>spicegarden292@gmail.com</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>182 Spice Garden Street, Ratnagiri, Ratnagiri</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Curry House</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>1059341021042</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Wardha</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>460026</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>04/06/2025</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Owner 484</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>9810222087</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>curryhouse56@gmail.com</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>145 Curry House Street, Wardha, Nagpur</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>The Golden Fork</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>1036334631221</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>412789</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2024</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Owner 238</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>9544663116</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>thegoldenfork315@gmail.com</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>246 The Golden Fork Street, Mumbai, Mumbai</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Tandoori Palace</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>1096521643277</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>487012</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2024</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>28/07/2025</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Owner 689</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>9938976835</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>tandooripalace101@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>283 Tandoori Palace Street, Aurangabad, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Tandoori Palace</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>1054581390401</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>471963</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>23/07/2024</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>23/07/2025</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Owner 306</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>9486744239</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>tandooripalace534@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>33 Tandoori Palace Street, Sangli, Sangli</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Flavors of India</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>1010209556003</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>412457</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>29/07/2025</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Owner 481</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>9969486874</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>flavorsofindia632@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>203 Flavors of India Street, Aurangabad, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Spice Route</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>1038591682862</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>433785</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>18/03/2025</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Owner 399</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>9551634688</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>spiceroute709@gmail.com</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>489 Spice Route Street, Ratnagiri, Ratnagiri</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Taj Mahal Restaurant</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>1098005003545</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Miraj</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>463569</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2024</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2025</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Owner 182</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>9137448763</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>tajmahalrestaur619@gmail.com</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>99 Taj Mahal Restaurant Street, Miraj, Sangli</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>The Golden Fork</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>1083261241342</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>456300</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2024</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Owner 98</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>9961160543</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>thegoldenfork353@gmail.com</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>19 The Golden Fork Street, Nagpur, Nagpur</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Flavors of India</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>1018693996436</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>435763</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2024</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2025</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Owner 703</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>9325270856</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>flavorsofindia341@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>237 Flavors of India Street, Mumbai, Mumbai</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Spice Route</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>1084142469348</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Paithan</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>434264</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2024</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2025</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Owner 35</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>9914819907</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>spiceroute238@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>245 Spice Route Street, Paithan, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Bombay Bites</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>1026808407721</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Wardha</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>479420</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>04/01/2025</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Owner 714</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>9634435914</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>bombaybites219@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>390 Bombay Bites Street, Wardha, Nagpur</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Delights</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>1010875898064</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Wardha</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>469660</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2024</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Owner 240</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>9736546629</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>coastaldelights682@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>23 Coastal Delights Street, Wardha, Nagpur</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Maharaja's Kitchen</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>1050195421532</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>489282</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2024</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2025</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Owner 271</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>9397557249</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>maharajaskitche544@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>56 Maharaja's Kitchen Street, Nagpur, Nagpur</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Flavors of India</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>1056190380118</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Malegaon</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>452278</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2025</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>22/07/2026</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Owner 901</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>9268551316</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>flavorsofindia3@gmail.com</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>231 Flavors of India Street, Malegaon, Nashik</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Flavors of India</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>1081898449013</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>464949</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2024</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2025</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Owner 195</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>9564679243</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>flavorsofindia484@gmail.com</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>403 Flavors of India Street, Satara, Satara</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Saffron Dreams</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1067804959302</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Catering</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>437690</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2024</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2025</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Owner 628</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>9180819607</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>saffrondreams12@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>57 Saffron Dreams Street, Navi Mumbai, Mumbai</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtrian Cuisine</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1074570063318</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Ichalkaranji</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>455941</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>14/02/2025</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>14/02/2026</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Owner 295</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>9837361145</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>maharashtriancu560@gmail.com</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>424 Maharashtrian Cuisine Street, Ichalkaranji, Kolhapur</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Taj Mahal Restaurant</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1051285212219</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>474684</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Owner 878</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>9139611797</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>tajmahalrestaur788@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>462 Taj Mahal Restaurant Street, Pune, Pune</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Delights</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1054969536811</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Food Truck</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>474484</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>11/02/2027</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Owner 688</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>9715287879</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>coastaldelights301@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>172 Coastal Delights Street, Aurangabad, Aurangabad</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Bombay Bites</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1075080873605</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Food Truck</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Pandharpur</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>440932</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>16/05/2024</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>16/05/2025</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Owner 141</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>9295944888</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>bombaybites819@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>136 Bombay Bites Street, Pandharpur, Solapur</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Taj Mahal Restaurant</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1044466430361</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>449231</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2024</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Owner 479</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>9678647906</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>tajmahalrestaur830@outlook.com</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>219 Taj Mahal Restaurant Street, Nagpur, Nagpur</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Maharaja's Kitchen</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>1028640385987</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Malegaon</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>428520</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>29/04/2024</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>29/04/2025</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Owner 612</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>9582784037</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>maharajaskitche608@gmail.com</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>239 Maharaja's Kitchen Street, Malegaon, Nashik</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Royal Feast</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>1023943535773</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>484345</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>08/08/2024</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Owner 938</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>9742822576</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>royalfeast119@outlook.com</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>165 Royal Feast Street, Mumbai, Mumbai</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Spice Route</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>1046171872100</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Food Truck</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Miraj</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>419490</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2025</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Owner 263</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>9664736716</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>spiceroute822@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>180 Spice Route Street, Miraj, Sangli</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Bombay Bites</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1077385671562</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>452677</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>24/03/2025</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Owner 440</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>9664515883</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>bombaybites564@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>302 Bombay Bites Street, Solapur, Solapur</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai Masala</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>1080230454559</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Malegaon</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>497237</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Owner 626</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>9458323535</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>mumbaimasala536@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>193 Mumbai Masala Street, Malegaon, Nashik</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Delights</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>1083354172159</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Karad</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>493398</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>29/07/2024</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>29/07/2025</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Owner 777</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>9544068939</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>coastaldelights828@yahoo.com</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>12 Coastal Delights Street, Karad, Satara</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Flavors of India</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>1030551483941</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>442624</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>09/05/2024</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>09/05/2025</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Owner 207</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>9842942780</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>flavorsofindia857@outlook.com</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>372 Flavors of India Street, Navi Mumbai, Mumbai</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Spice Garden</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>1079039098961</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Miraj</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>421350</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>29/12/2024</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>29/12/2025</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Owner 525</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>9380848126</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>spicegarden267@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>431 Spice Garden Street, Miraj, Sangli</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Taj Mahal Restaurant</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567890</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>400001</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>15/03/2023</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>14/03/2024</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>tajmahal@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>123 Marine Drive Mumbai</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Spice Garden</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567891</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>411001</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2022</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2025</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Priya Sharma</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>9876543211</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>spicegarden@email.com</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>456 MG Road Pune</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai Masala</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567892</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Fast Food</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>400601</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>10/01/2024</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2025</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Amit Patel</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>9876543212</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>mumbaimasala@food.com</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>789 Thane West</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Delights</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567893</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>415612</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>25/07/2023</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>24/07/2024</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Singh</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>9876543213</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>coastal@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>321 Beach Road Ratnagiri</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Maharaja's Kitchen</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567894</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>440001</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>12/02/2023</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>11/02/2026</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>9876543214</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>maharaja@cafe.com</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>654 Sitabuldi Nagpur</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Flavors of India</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567895</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Cloud Kitchen</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Pimpri-Chinchwad</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>411044</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>08/11/2023</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>07/11/2024</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Suresh Desai</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>9876543215</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>flavors@kitchen.com</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>987 Chinchwad Pune</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>The Golden Fork</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567896</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>431001</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>30/04/2022</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>29/04/2025</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Deepak Joshi</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>9876543216</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>goldenfork@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>147 Jalna Road Aurangabad</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Curry House</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567897</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>422001</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>18/06/2023</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>17/06/2024</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>Anita Verma</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>9876543217</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>curry@house.com</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>258 Nashik Road</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Tandoori Palace</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567898</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>416001</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2024</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Ramesh Kulkarni</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>9876543218</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>tandoori@palace.com</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>369 Kolhapur City</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Bombay Bites</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567899</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Fast Food</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>400706</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>05/08/2022</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Kavya Reddy</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>9876543219</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>bombay@bites.com</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>741 Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Saffron Dreams</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567900</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>413001</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>14/03/2023</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Mohit Sharma</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>9876543220</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>saffron@dreams.com</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>852 Solapur City</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Royal Feast</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567901</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>416416</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>27/10/2023</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2024</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Pradeep Nair</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>9876543221</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>royal@feast.com</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>963 Sangli Town</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Namaste Kitchen</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567902</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>415001</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>11/01/2024</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>10/01/2025</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Sneha Iyer</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>9876543222</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>namaste@kitchen.com</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>147 Satara City</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Spice Route</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567903</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Chiplun</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>415605</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2023</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Arjun Menon</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>9876543223</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>spice@route.com</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>258 Chiplun Town</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtrian Cuisine</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567904</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Paithan</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>431204</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>06/12/2023</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>05/12/2024</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>Divya Sharma</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>9876543224</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>maharashtrian@cuisine.com</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>369 Paithan Road</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Kitchen</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567905</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>415612</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>23/02/2024</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>22/02/2025</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Rohan Desai</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>9876543225</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>coastal@kitchen.com</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>741 Ratnagiri Beach</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Urban Eats</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567906</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Fast Food</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>411002</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2023</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Zara Khan</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>9876543226</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>urban@eats.com</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>852 Pune Downtown</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Heritage Restaurant</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567907</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>FSSAI Registration</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>440002</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2023</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2024</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Patel</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>9876543227</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>heritage@restaurant.com</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>963 Nagpur City</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Fusion Flavors</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567908</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Central License</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>400002</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>28/11/2023</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>27/11/2024</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>Priya Nair</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>9876543228</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>fusion@flavors.com</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>147 Mumbai Central</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Garden Bistro</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>10AABCT1234567909</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>State License</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Ichalkaranji</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>416115</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>13/08/2023</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>Anil Sharma</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>9876543229</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>garden@bistro.com</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>258 Ichalkaranji</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7040,7 +12080,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09T00:45:01.854715</t>
+          <t>2026-04-09T13:47:00.460061</t>
         </is>
       </c>
     </row>
@@ -7051,7 +12091,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
@@ -7061,7 +12101,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -7081,7 +12121,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
